--- a/16.07.26/report-16.07.26.xlsx
+++ b/16.07.26/report-16.07.26.xlsx
@@ -60,7 +60,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,17 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F9D58"/>
+        <fgColor rgb="0000B87A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007C3AED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000B87A"/>
+        <fgColor rgb="000F9D58"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,9 +126,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,28 +500,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sarbon Admin — Drivers &amp; Dispatchers · 16.07.2026</t>
+          <t>Sarbon — Company workspace + Admin moderation · 16.07.2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Account status «No data» → effective; activate bug fixed; Account/KYC/Moderation editable in Edit drawer; actions slimmed to View/Edit/Delete.</t>
+          <t>New /company workspace (17 sections, invitations/roles/fleet/finance, invite-accept + group chat) + admin moderation-log timestamps + Drivers/Dispatchers effective Account status. 145 files / 3 commits.</t>
         </is>
       </c>
     </row>
@@ -565,227 +557,291 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Company / Workspace</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>/company/:id turned from a Profile|Cargo toggle into a 17-section grouped sidebar; each section = lazy chunk + pure companyX.ts + unit test, gated by me/permissions</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>GET /v1/companies/:id, /me/permissions</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>company-overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Company / Team</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Invitations (create/list/resend/revoke), employees (role change, per-key permission grant/deny/inherit, remove), roles (retroactive permission overlays)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>/companies/:id/{invitations,users,roles}</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>company-employees, -invitations, -roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Company / Fleet</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Power + trailer plates CRUD with maintenance start/complete, assignments, maintenance journal, drivers roster (forbidden for SHIPPER)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>/companies/:id/fleet/*, /drivers</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>company-vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Company / Operations</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Company cargo (all statuses), trips (filters + curator-manager assign), finance summary by currency (no FX — profit within one currency)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>/companies/:id/{cargo,trips,finance/summary}</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>company-trips, -finance, -cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Company / Invite + Chat</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Invitee side: /accept-invite?token= root page + one-shot breadcrumb through login; chat section launches the company group into the main /chat</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>/v1/invitations/accept, /companies/:id/group</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
           <t>FIX</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Root cause</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>FE rendered raw nullable account_status; used effective_status (COALESCE→active) instead</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Driver.effective_status</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Company / Profile + antd</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>"My companies" section (list + switch active company); AntdProvider maps uz -&gt; uz_UZ (was en_US, leaking English antd chrome)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>CompanyProfileCompanies, AntdProvider</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FEATURE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Admin / Moderation log</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Separate requested_at + decided_at columns in the moderation log (was a single created_at "Date")</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>GET /v1/admin/moderation/log</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>FIX</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Drivers</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Account column shows effective status — no more "No data"; also feeds sort/filter/isBlocked</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>GET /v1/admin/drivers</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>01, 05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Drivers + Dispatchers</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Actions column slimmed to View / Edit / Delete; "Send to moderation" removed from the row</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>02, 07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>FEATURE</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Drivers</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Account / KYC / Moderation editable inside the Edit drawer (AdminDriverStatusEditor)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>/kyc/accept·reject, /moderation/approve·reject·resubmit</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Admin / Drivers</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Account column shows effective_status (null -&gt; Active, no more "No data"); actions slimmed to View/Edit/Delete; Account/KYC/Moderation editable in the Edit drawer; activate no longer offered on an already-active row</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>GET /v1/admin/drivers, /kyc/*, /moderation/*</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>01, 03, 04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>FIX</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Drivers</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Activate no longer offered on an already-active row (was 400 on null); resubmit gated to rejected</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>/moderation/{activate,inactive,resubmit}</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Dispatchers</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Edit drawer moderation section keyed on moderation_status; isBlocked read from moderation_status</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>/moderation/{activate,inactive,block,unblock,resubmit}</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Admin / Dispatchers</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Same pattern keyed on moderation_status (dispatcher account_status is hard-coded active); isBlocked read from moderation_status</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>/v1/admin/dispatchers/moderation/*</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>06, 08, 09, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>i18n</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>New keys resubmitOnlyRejected + accountMenuLabel across all 15 locales</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>admin.moderationActions.*</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -803,27 +859,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Verification gates</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -835,7 +891,7 @@
           <t>pnpm build (tsc -b + vite)</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>exit 0</t>
         </is>
@@ -847,7 +903,7 @@
           <t>eslint --max-warnings 0 (changed files)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>clean</t>
         </is>
@@ -859,7 +915,7 @@
           <t>vitest run</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>1754 / 1754 (165 files)</t>
         </is>
@@ -868,36 +924,60 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Locale parity</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>2 new keys × 15 locales</t>
+          <t>Company workspace (qa/verify-company-workspace.mjs)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>17/17 sections, 0 raw i18n keys</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Live run (staging, admin login)</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>10 screenshots, behaviour confirmed</t>
+          <t>Accept-invite (qa/verify-accept-invite.mjs)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>7/7 states</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Locale parity</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>15/15 (company.* en/uz/ru + placeholders)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Live run (staging, admin login)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>10 screenshots, behaviour confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Files changed</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>145 (3 commits)</t>
         </is>
       </c>
     </row>
